--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>R$ 9.960,20</t>
-  </si>
-  <si>
-    <t>105.0</t>
-  </si>
-  <si>
-    <t>71.1</t>
-  </si>
-  <si>
-    <t>7.26</t>
-  </si>
-  <si>
-    <t>23.1</t>
-  </si>
-  <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>27.7%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 9.770,71</t>
+  </si>
+  <si>
+    <t>101.9</t>
+  </si>
+  <si>
+    <t>69.5</t>
+  </si>
+  <si>
+    <t>7.17</t>
+  </si>
+  <si>
+    <t>23.2</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>27.4%</t>
+  </si>
+  <si>
+    <t>15.9%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -971,55 +971,55 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
+    <t>3.0%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.2%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>1777.0</t>
-  </si>
-  <si>
-    <t>1493.0</t>
-  </si>
-  <si>
-    <t>113.0</t>
-  </si>
-  <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>286.0</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>541.0</t>
-  </si>
-  <si>
-    <t>218.0</t>
-  </si>
-  <si>
-    <t>407.0</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>85.0</t>
+    <t>5.6%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>2411.0</t>
+  </si>
+  <si>
+    <t>2020.0</t>
+  </si>
+  <si>
+    <t>145.0</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>378.0</t>
+  </si>
+  <si>
+    <t>137.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>707.0</t>
+  </si>
+  <si>
+    <t>292.0</t>
+  </si>
+  <si>
+    <t>614.0</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>114.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2206,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,35 +2236,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>17017.27</v>
+      </c>
+      <c r="N6" s="6">
+        <v>163</v>
+      </c>
+      <c r="O6" s="6">
+        <v>135</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.9955484472049694</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.946542962962964</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.1491159090909089</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.40740740740740738</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.059259259259259262</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -2925,7 +2983,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2955,35 +3013,93 @@
         <v>58</v>
       </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="6"/>
+      <c r="M11" s="5">
+        <v>14544.200000000001</v>
+      </c>
+      <c r="N11" s="6">
+        <v>144</v>
+      </c>
+      <c r="O11" s="6">
+        <v>113</v>
+      </c>
+      <c r="P11" s="7">
+        <v>6.5719909722222223</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>19.043510619469028</v>
+      </c>
+      <c r="R11" s="8">
+        <v>6.5875378378378375</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0.26548672566371684</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.21238938053097345</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0.017699115044247787</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0.035398230088495575</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0.017699115044247787</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0.026548672566371681</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0.026548672566371681</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0.1415929203539823</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>31</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>24</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0.0088495575221238937</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP11" s="4">
         <v>58</v>
       </c>
@@ -3181,7 +3297,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3211,35 +3327,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>14474.139999999999</v>
+      </c>
+      <c r="N13" s="6">
+        <v>151</v>
+      </c>
+      <c r="O13" s="6">
+        <v>109</v>
+      </c>
+      <c r="P13" s="7">
+        <v>12.627527096774193</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>27.430887155963301</v>
+      </c>
+      <c r="R13" s="8">
+        <v>6.6518348623853205</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.082568807339449546</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.1743119266055046</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.0091743119266055051</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.0091743119266055051</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.03669724770642202</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>21</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.11926605504587157</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>13</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -3588,7 +3762,7 @@
         <v>19520</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>51</v>
@@ -3618,35 +3792,93 @@
         <v>58</v>
       </c>
       <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="6"/>
-      <c r="AL16" s="6"/>
-      <c r="AM16" s="6"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="6"/>
+      <c r="M16" s="5">
+        <v>3226.8499999999999</v>
+      </c>
+      <c r="N16" s="6">
+        <v>35</v>
+      </c>
+      <c r="O16" s="6">
+        <v>13</v>
+      </c>
+      <c r="P16" s="7">
+        <v>7.5761914285714287</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>23.410609090909091</v>
+      </c>
+      <c r="R16" s="8">
+        <v>10.9</v>
+      </c>
+      <c r="S16" s="8">
+        <v>7</v>
+      </c>
+      <c r="T16" s="9">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="W16" s="9">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE16" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP16" s="4">
         <v>58</v>
       </c>
@@ -3687,7 +3919,7 @@
         <v>19521</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>51</v>
@@ -3717,8 +3949,12 @@
         <v>58</v>
       </c>
       <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="6"/>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
       <c r="O17" s="6"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="8"/>
@@ -5296,7 +5532,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5326,35 +5562,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>6707.0500000000002</v>
+      </c>
+      <c r="N28" s="6">
+        <v>76</v>
+      </c>
+      <c r="O28" s="6">
+        <v>47</v>
+      </c>
+      <c r="P28" s="7">
+        <v>1.9050232876712327</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>16.395036170212766</v>
+      </c>
+      <c r="R28" s="8">
+        <v>7.6624106382978727</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.57446808510638303</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.042553191489361701</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>13</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -6023,7 +6317,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>51</v>
@@ -6051,35 +6345,93 @@
         <v>58</v>
       </c>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="6"/>
-      <c r="AM33" s="6"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="6"/>
+      <c r="M33" s="5">
+        <v>12450.16</v>
+      </c>
+      <c r="N33" s="6">
+        <v>117</v>
+      </c>
+      <c r="O33" s="6">
+        <v>76</v>
+      </c>
+      <c r="P33" s="7">
+        <v>2.3084033613445376</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>15.594078947368422</v>
+      </c>
+      <c r="R33" s="8">
+        <v>6.5875560000000002</v>
+      </c>
+      <c r="S33" s="8">
+        <v>7</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0.55263157894736847</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.19736842105263158</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0.092105263157894732</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0.013157894736842105</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0.065789473684210523</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>5</v>
+      </c>
       <c t="s" r="AP33" s="4">
         <v>58</v>
       </c>
@@ -6679,7 +7031,7 @@
         <v>6.3991556962025316</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>0.48148148148148145</v>
@@ -6787,7 +7139,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6817,35 +7169,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>13968.049999999999</v>
+      </c>
+      <c r="N39" s="6">
+        <v>157</v>
+      </c>
+      <c r="O39" s="6">
+        <v>114</v>
+      </c>
+      <c r="P39" s="7">
+        <v>3.9988398734177215</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>30.088157894736845</v>
+      </c>
+      <c r="R39" s="8">
+        <v>18.412649107142858</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.11403508771929824</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0.0087719298239999997</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.043859649122807015</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7299,7 +7709,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7329,35 +7739,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>9222.3500000000004</v>
+      </c>
+      <c r="N43" s="6">
+        <v>94</v>
+      </c>
+      <c r="O43" s="6">
+        <v>65</v>
+      </c>
+      <c r="P43" s="7">
+        <v>7.2464915789473681</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>35.029487692307697</v>
+      </c>
+      <c r="R43" s="8">
+        <v>21.547090476190476</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.046153846153846156</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.046153846153846156</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8334,7 +8802,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8364,35 +8832,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>13364.43</v>
+      </c>
+      <c r="N50" s="6">
+        <v>143</v>
+      </c>
+      <c r="O50" s="6">
+        <v>106</v>
+      </c>
+      <c r="P50" s="7">
+        <v>3.1914916083916087</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>19.409591509433966</v>
+      </c>
+      <c r="R50" s="8">
+        <v>8.3577780952380945</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.25471698113207547</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.21698113207547171</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.009433962264150943</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.009433962264150943</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0.009433962264150943</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.16981132075471697</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>18</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -9001,7 +9527,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9031,35 +9557,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>7906.2399999999998</v>
+      </c>
+      <c r="N55" s="6">
+        <v>94</v>
+      </c>
+      <c r="O55" s="6">
+        <v>76</v>
+      </c>
+      <c r="P55" s="7">
+        <v>3.3388367924528302</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>24.55811447368421</v>
+      </c>
+      <c r="R55" s="8">
+        <v>14.281140789473685</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.14473684210526316</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.17105263157894737</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.11842105263157894</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0.013157894736842105</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.039473684210526314</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9978,7 +10562,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -10008,35 +10592,93 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="M62" s="5">
+        <v>12816.09</v>
+      </c>
+      <c r="N62" s="6">
+        <v>120</v>
+      </c>
+      <c r="O62" s="6">
+        <v>81</v>
+      </c>
+      <c r="P62" s="7">
+        <v>3.8439262711864406</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>18.084774074074076</v>
+      </c>
+      <c r="R62" s="8">
+        <v>7.38396582278481</v>
+      </c>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.34567901234567899</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.061728395061728392</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.024691358024691357</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0.012345679012345678</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.024691358024691357</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0.024691358024691357</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -10957,7 +11599,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>51</v>
@@ -10985,35 +11627,93 @@
         <v>58</v>
       </c>
       <c r="L69" s="4"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="8"/>
-      <c r="R69" s="8"/>
-      <c r="S69" s="8"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="9"/>
-      <c r="V69" s="9"/>
-      <c r="W69" s="9"/>
-      <c r="X69" s="9"/>
-      <c r="Y69" s="9"/>
-      <c r="Z69" s="9"/>
-      <c r="AA69" s="9"/>
-      <c r="AB69" s="9"/>
-      <c r="AC69" s="9"/>
-      <c r="AD69" s="6"/>
-      <c r="AE69" s="6"/>
-      <c r="AF69" s="6"/>
-      <c r="AG69" s="6"/>
-      <c r="AH69" s="6"/>
-      <c r="AI69" s="6"/>
-      <c r="AJ69" s="6"/>
-      <c r="AK69" s="6"/>
-      <c r="AL69" s="6"/>
-      <c r="AM69" s="6"/>
-      <c r="AN69" s="9"/>
-      <c r="AO69" s="6"/>
+      <c r="M69" s="5">
+        <v>9237.0599999999995</v>
+      </c>
+      <c r="N69" s="6">
+        <v>107</v>
+      </c>
+      <c r="O69" s="6">
+        <v>83</v>
+      </c>
+      <c r="P69" s="7">
+        <v>3.3833330275229359</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>16.04196746987952</v>
+      </c>
+      <c r="R69" s="8">
+        <v>5.1746913580246909</v>
+      </c>
+      <c r="S69" s="8">
+        <v>8</v>
+      </c>
+      <c r="T69" s="9">
+        <v>0.45783132530120479</v>
+      </c>
+      <c r="U69" s="9">
+        <v>0.16867469879518071</v>
+      </c>
+      <c r="V69" s="9">
+        <v>0</v>
+      </c>
+      <c r="W69" s="9">
+        <v>0</v>
+      </c>
+      <c r="X69" s="9">
+        <v>0.060240963855421686</v>
+      </c>
+      <c r="Y69" s="9">
+        <v>0.024096385542168676</v>
+      </c>
+      <c r="Z69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="9">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="AB69" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="9">
+        <v>0.024096385542168676</v>
+      </c>
+      <c r="AD69" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI69" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN69" s="9">
+        <v>0.060240963855421686</v>
+      </c>
+      <c r="AO69" s="6">
+        <v>5</v>
+      </c>
       <c t="s" r="AP69" s="4">
         <v>58</v>
       </c>
@@ -11211,7 +11911,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11239,35 +11939,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>16315.23</v>
+      </c>
+      <c r="N71" s="6">
+        <v>182</v>
+      </c>
+      <c r="O71" s="6">
+        <v>103</v>
+      </c>
+      <c r="P71" s="7">
+        <v>3.3058988764044948</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>15.562459223300969</v>
+      </c>
+      <c r="R71" s="8">
+        <v>4.3514999999999997</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.44660194174757284</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.12621359223300971</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.019417475728155338</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0.0097087378640000003</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.029126213592233011</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.019417475728155338</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.077669902912621352</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.029126213592233011</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11715,7 +12473,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11745,35 +12503,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>6656.6999999999998</v>
+      </c>
+      <c r="N75" s="6">
+        <v>72</v>
+      </c>
+      <c r="O75" s="6">
+        <v>42</v>
+      </c>
+      <c r="P75" s="7">
+        <v>3.7342597222222218</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>23.240078571428572</v>
+      </c>
+      <c r="R75" s="8">
+        <v>13.059348780487806</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -11814,7 +12630,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -11842,35 +12658,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>5624.9099999999999</v>
+      </c>
+      <c r="N76" s="6">
+        <v>67</v>
+      </c>
+      <c r="O76" s="6">
+        <v>32</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.4316176470588236</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>19.718228125</v>
+      </c>
+      <c r="R76" s="8">
+        <v>7.0390625</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.3125</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.09375</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -16113,7 +16987,7 @@
         <v>19722</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C105" s="4">
         <v>51</v>
@@ -16141,35 +17015,93 @@
         <v>58</v>
       </c>
       <c r="L105" s="4"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="6"/>
-      <c r="O105" s="6"/>
-      <c r="P105" s="7"/>
-      <c r="Q105" s="8"/>
-      <c r="R105" s="8"/>
-      <c r="S105" s="8"/>
-      <c r="T105" s="9"/>
-      <c r="U105" s="9"/>
-      <c r="V105" s="9"/>
-      <c r="W105" s="9"/>
-      <c r="X105" s="9"/>
-      <c r="Y105" s="9"/>
-      <c r="Z105" s="9"/>
-      <c r="AA105" s="9"/>
-      <c r="AB105" s="9"/>
-      <c r="AC105" s="9"/>
-      <c r="AD105" s="6"/>
-      <c r="AE105" s="6"/>
-      <c r="AF105" s="6"/>
-      <c r="AG105" s="6"/>
-      <c r="AH105" s="6"/>
-      <c r="AI105" s="6"/>
-      <c r="AJ105" s="6"/>
-      <c r="AK105" s="6"/>
-      <c r="AL105" s="6"/>
-      <c r="AM105" s="6"/>
-      <c r="AN105" s="9"/>
-      <c r="AO105" s="6"/>
+      <c r="M105" s="5">
+        <v>6414.6199999999999</v>
+      </c>
+      <c r="N105" s="6">
+        <v>59</v>
+      </c>
+      <c r="O105" s="6">
+        <v>49</v>
+      </c>
+      <c r="P105" s="7">
+        <v>4.7722222222222221</v>
+      </c>
+      <c r="Q105" s="8">
+        <v>23.244218367346939</v>
+      </c>
+      <c r="R105" s="8">
+        <v>14.38939318181818</v>
+      </c>
+      <c r="S105" s="8">
+        <v>6.2999999999999998</v>
+      </c>
+      <c r="T105" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U105" s="9">
+        <v>0.40816326530612246</v>
+      </c>
+      <c r="V105" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="W105" s="9">
+        <v>0</v>
+      </c>
+      <c r="X105" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Y105" s="9">
+        <v>0.061224489795918366</v>
+      </c>
+      <c r="Z105" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AA105" s="9">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="AB105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="9">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="AD105" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF105" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH105" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI105" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK105" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM105" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN105" s="9">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AO105" s="6">
+        <v>4</v>
+      </c>
       <c t="s" r="AP105" s="4">
         <v>58</v>
       </c>
@@ -17286,7 +18218,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>51</v>
@@ -17316,35 +18248,93 @@
         <v>58</v>
       </c>
       <c r="L114" s="4"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="6"/>
-      <c r="O114" s="6"/>
-      <c r="P114" s="7"/>
-      <c r="Q114" s="8"/>
-      <c r="R114" s="8"/>
-      <c r="S114" s="8"/>
-      <c r="T114" s="9"/>
-      <c r="U114" s="9"/>
-      <c r="V114" s="9"/>
-      <c r="W114" s="9"/>
-      <c r="X114" s="9"/>
-      <c r="Y114" s="9"/>
-      <c r="Z114" s="9"/>
-      <c r="AA114" s="9"/>
-      <c r="AB114" s="9"/>
-      <c r="AC114" s="9"/>
-      <c r="AD114" s="6"/>
-      <c r="AE114" s="6"/>
-      <c r="AF114" s="6"/>
-      <c r="AG114" s="6"/>
-      <c r="AH114" s="6"/>
-      <c r="AI114" s="6"/>
-      <c r="AJ114" s="6"/>
-      <c r="AK114" s="6"/>
-      <c r="AL114" s="6"/>
-      <c r="AM114" s="6"/>
-      <c r="AN114" s="9"/>
-      <c r="AO114" s="6"/>
+      <c r="M114" s="5">
+        <v>21524.689999999999</v>
+      </c>
+      <c r="N114" s="6">
+        <v>184</v>
+      </c>
+      <c r="O114" s="6">
+        <v>143</v>
+      </c>
+      <c r="P114" s="7">
+        <v>10.628218518518519</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>25.299650349650349</v>
+      </c>
+      <c r="R114" s="8">
+        <v>6.6335746376811597</v>
+      </c>
+      <c r="S114" s="8">
+        <v>8</v>
+      </c>
+      <c r="T114" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="U114" s="9">
+        <v>0.3776223776223776</v>
+      </c>
+      <c r="V114" s="9">
+        <v>0.027972027972027972</v>
+      </c>
+      <c r="W114" s="9">
+        <v>0</v>
+      </c>
+      <c r="X114" s="9">
+        <v>0.034965034965034968</v>
+      </c>
+      <c r="Y114" s="9">
+        <v>0.027972027972027972</v>
+      </c>
+      <c r="Z114" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="9">
+        <v>0.069930069930069935</v>
+      </c>
+      <c r="AB114" s="9">
+        <v>0.062937062937062943</v>
+      </c>
+      <c r="AC114" s="9">
+        <v>0.25174825174825177</v>
+      </c>
+      <c r="AD114" s="6">
+        <v>69</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>54</v>
+      </c>
+      <c r="AF114" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG114" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH114" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI114" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ114" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK114" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL114" s="6">
+        <v>9</v>
+      </c>
+      <c r="AM114" s="6">
+        <v>36</v>
+      </c>
+      <c r="AN114" s="9">
+        <v>0.006993006993006993</v>
+      </c>
+      <c r="AO114" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP114" s="4">
         <v>58</v>
       </c>
@@ -17639,7 +18629,7 @@
         <v>19745</v>
       </c>
       <c r="B117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C117" s="4">
         <v>51</v>
@@ -17669,35 +18659,93 @@
         <v>58</v>
       </c>
       <c r="L117" s="4"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="6"/>
-      <c r="O117" s="6"/>
-      <c r="P117" s="7"/>
-      <c r="Q117" s="8"/>
-      <c r="R117" s="8"/>
-      <c r="S117" s="8"/>
-      <c r="T117" s="9"/>
-      <c r="U117" s="9"/>
-      <c r="V117" s="9"/>
-      <c r="W117" s="9"/>
-      <c r="X117" s="9"/>
-      <c r="Y117" s="9"/>
-      <c r="Z117" s="9"/>
-      <c r="AA117" s="9"/>
-      <c r="AB117" s="9"/>
-      <c r="AC117" s="9"/>
-      <c r="AD117" s="6"/>
-      <c r="AE117" s="6"/>
-      <c r="AF117" s="6"/>
-      <c r="AG117" s="6"/>
-      <c r="AH117" s="6"/>
-      <c r="AI117" s="6"/>
-      <c r="AJ117" s="6"/>
-      <c r="AK117" s="6"/>
-      <c r="AL117" s="6"/>
-      <c r="AM117" s="6"/>
-      <c r="AN117" s="9"/>
-      <c r="AO117" s="6"/>
+      <c r="M117" s="5">
+        <v>7290.3000000000002</v>
+      </c>
+      <c r="N117" s="6">
+        <v>74</v>
+      </c>
+      <c r="O117" s="6">
+        <v>56</v>
+      </c>
+      <c r="P117" s="7">
+        <v>6.618115942028985</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>20.416964285714283</v>
+      </c>
+      <c r="R117" s="8">
+        <v>13.856861764705883</v>
+      </c>
+      <c r="S117" s="8">
+        <v>7</v>
+      </c>
+      <c r="T117" s="9">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="U117" s="9">
+        <v>0.7321428571428571</v>
+      </c>
+      <c r="V117" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="W117" s="9">
+        <v>0</v>
+      </c>
+      <c r="X117" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="Y117" s="9">
+        <v>0.089285714285714288</v>
+      </c>
+      <c r="Z117" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="9">
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="AB117" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="AC117" s="9">
+        <v>0.39285714285714285</v>
+      </c>
+      <c r="AD117" s="6">
+        <v>60</v>
+      </c>
+      <c r="AE117" s="6">
+        <v>41</v>
+      </c>
+      <c r="AF117" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH117" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI117" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ117" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK117" s="6">
+        <v>23</v>
+      </c>
+      <c r="AL117" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM117" s="6">
+        <v>22</v>
+      </c>
+      <c r="AN117" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO117" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP117" s="4">
         <v>58</v>
       </c>
@@ -18988,7 +20036,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -19018,35 +20066,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>0</v>
+      </c>
+      <c r="N126" s="6">
+        <v>51</v>
+      </c>
+      <c r="O126" s="6">
+        <v>40</v>
+      </c>
+      <c r="P126" s="7">
+        <v>6.132025490196078</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>30.3491675</v>
+      </c>
+      <c r="R126" s="8">
+        <v>17.3070825</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -20029,7 +21135,7 @@
         <v>19775</v>
       </c>
       <c r="B133" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C133" s="4">
         <v>51</v>
@@ -20059,35 +21165,93 @@
         <v>58</v>
       </c>
       <c r="L133" s="4"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="6"/>
-      <c r="O133" s="6"/>
-      <c r="P133" s="7"/>
-      <c r="Q133" s="8"/>
-      <c r="R133" s="8"/>
-      <c r="S133" s="8"/>
-      <c r="T133" s="9"/>
-      <c r="U133" s="9"/>
-      <c r="V133" s="9"/>
-      <c r="W133" s="9"/>
-      <c r="X133" s="9"/>
-      <c r="Y133" s="9"/>
-      <c r="Z133" s="9"/>
-      <c r="AA133" s="9"/>
-      <c r="AB133" s="9"/>
-      <c r="AC133" s="9"/>
-      <c r="AD133" s="6"/>
-      <c r="AE133" s="6"/>
-      <c r="AF133" s="6"/>
-      <c r="AG133" s="6"/>
-      <c r="AH133" s="6"/>
-      <c r="AI133" s="6"/>
-      <c r="AJ133" s="6"/>
-      <c r="AK133" s="6"/>
-      <c r="AL133" s="6"/>
-      <c r="AM133" s="6"/>
-      <c r="AN133" s="9"/>
-      <c r="AO133" s="6"/>
+      <c r="M133" s="5">
+        <v>8037.4799999999996</v>
+      </c>
+      <c r="N133" s="6">
+        <v>81</v>
+      </c>
+      <c r="O133" s="6">
+        <v>53</v>
+      </c>
+      <c r="P133" s="7">
+        <v>4.4739211764705882</v>
+      </c>
+      <c r="Q133" s="8">
+        <v>14.41474423076923</v>
+      </c>
+      <c r="R133" s="8">
+        <v>8.1960794117647051</v>
+      </c>
+      <c r="S133" s="8">
+        <v>7</v>
+      </c>
+      <c r="T133" s="9">
+        <v>0.55769230769230771</v>
+      </c>
+      <c r="U133" s="9">
+        <v>0.58490566037735847</v>
+      </c>
+      <c r="V133" s="9">
+        <v>0</v>
+      </c>
+      <c r="W133" s="9">
+        <v>0</v>
+      </c>
+      <c r="X133" s="9">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="Y133" s="9">
+        <v>0.11320754716981132</v>
+      </c>
+      <c r="Z133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="9">
+        <v>0.39622641509433965</v>
+      </c>
+      <c r="AB133" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="AC133" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="AD133" s="6">
+        <v>39</v>
+      </c>
+      <c r="AE133" s="6">
+        <v>31</v>
+      </c>
+      <c r="AF133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI133" s="6">
+        <v>6</v>
+      </c>
+      <c r="AJ133" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="6">
+        <v>21</v>
+      </c>
+      <c r="AL133" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM133" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO133" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP133" s="4">
         <v>58</v>
       </c>
@@ -20442,7 +21606,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -20472,35 +21636,93 @@
         <v>58</v>
       </c>
       <c r="L136" s="4"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8"/>
-      <c r="S136" s="8"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="M136" s="5">
+        <v>8075.1999999999998</v>
+      </c>
+      <c r="N136" s="6">
+        <v>82</v>
+      </c>
+      <c r="O136" s="6">
+        <v>39</v>
+      </c>
+      <c r="P136" s="7">
+        <v>9.152880246913579</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>30.338033333333332</v>
+      </c>
+      <c r="R136" s="8">
+        <v>14.828071052631577</v>
+      </c>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
+      <c r="T136" s="9">
+        <v>0.12820512820512819</v>
+      </c>
+      <c r="U136" s="9">
+        <v>0.28205128205128205</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0.12820512820512819</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -21673,7 +22895,7 @@
         <v>19804</v>
       </c>
       <c r="B145" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C145" s="4">
         <v>51</v>
@@ -21703,35 +22925,93 @@
         <v>58</v>
       </c>
       <c r="L145" s="4"/>
-      <c r="M145" s="5"/>
-      <c r="N145" s="6"/>
-      <c r="O145" s="6"/>
-      <c r="P145" s="7"/>
-      <c r="Q145" s="8"/>
-      <c r="R145" s="8"/>
-      <c r="S145" s="8"/>
-      <c r="T145" s="9"/>
-      <c r="U145" s="9"/>
-      <c r="V145" s="9"/>
-      <c r="W145" s="9"/>
-      <c r="X145" s="9"/>
-      <c r="Y145" s="9"/>
-      <c r="Z145" s="9"/>
-      <c r="AA145" s="9"/>
-      <c r="AB145" s="9"/>
-      <c r="AC145" s="9"/>
-      <c r="AD145" s="6"/>
-      <c r="AE145" s="6"/>
-      <c r="AF145" s="6"/>
-      <c r="AG145" s="6"/>
-      <c r="AH145" s="6"/>
-      <c r="AI145" s="6"/>
-      <c r="AJ145" s="6"/>
-      <c r="AK145" s="6"/>
-      <c r="AL145" s="6"/>
-      <c r="AM145" s="6"/>
-      <c r="AN145" s="9"/>
-      <c r="AO145" s="6"/>
+      <c r="M145" s="5">
+        <v>6550.0699999999997</v>
+      </c>
+      <c r="N145" s="6">
+        <v>80</v>
+      </c>
+      <c r="O145" s="6">
+        <v>66</v>
+      </c>
+      <c r="P145" s="7">
+        <v>18.241250000000001</v>
+      </c>
+      <c r="Q145" s="8">
+        <v>25.337625757575758</v>
+      </c>
+      <c r="R145" s="8">
+        <v>2.0841463414634145</v>
+      </c>
+      <c r="S145" s="8">
+        <v>7</v>
+      </c>
+      <c r="T145" s="9">
+        <v>0.37878787878787878</v>
+      </c>
+      <c r="U145" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V145" s="9">
+        <v>0</v>
+      </c>
+      <c r="W145" s="9">
+        <v>0</v>
+      </c>
+      <c r="X145" s="9">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="Y145" s="9">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="Z145" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="9">
+        <v>0.53030303030303028</v>
+      </c>
+      <c r="AB145" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AC145" s="9">
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="AD145" s="6">
+        <v>55</v>
+      </c>
+      <c r="AE145" s="6">
+        <v>44</v>
+      </c>
+      <c r="AF145" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG145" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI145" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ145" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK145" s="6">
+        <v>35</v>
+      </c>
+      <c r="AL145" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM145" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN145" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO145" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP145" s="4">
         <v>58</v>
       </c>
@@ -23536,7 +24816,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -23566,35 +24846,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>5461.9799999999996</v>
+      </c>
+      <c r="N158" s="6">
+        <v>51</v>
+      </c>
+      <c r="O158" s="6">
+        <v>42</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.6088235294117652</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>19.572221428571432</v>
+      </c>
+      <c r="R158" s="8">
+        <v>5.5535714285714288</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -23696,7 +25034,7 @@
         <v>0.011494252873563218</v>
       </c>
       <c r="W159" s="9">
-        <v>0</v>
+        <v>0.022988505746999999</v>
       </c>
       <c r="X159" s="9">
         <v>0.011494252873563218</v>
@@ -23726,7 +25064,7 @@
         <v>1</v>
       </c>
       <c r="AG159" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH159" s="6">
         <v>1</v>
@@ -24098,7 +25436,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24128,35 +25466,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>7543.7399999999998</v>
+      </c>
+      <c r="N162" s="6">
+        <v>86</v>
+      </c>
+      <c r="O162" s="6">
+        <v>42</v>
+      </c>
+      <c r="P162" s="7">
+        <v>7.3329222222222219</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>21.312302380952381</v>
+      </c>
+      <c r="R162" s="8">
+        <v>6.2849585365853651</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0.047619047619000002</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>12</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -24610,7 +26006,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -24640,35 +26036,93 @@
         <v>58</v>
       </c>
       <c r="L166" s="4"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="6"/>
-      <c r="O166" s="6"/>
-      <c r="P166" s="7"/>
-      <c r="Q166" s="8"/>
-      <c r="R166" s="8"/>
-      <c r="S166" s="8"/>
-      <c r="T166" s="9"/>
-      <c r="U166" s="9"/>
-      <c r="V166" s="9"/>
-      <c r="W166" s="9"/>
-      <c r="X166" s="9"/>
-      <c r="Y166" s="9"/>
-      <c r="Z166" s="9"/>
-      <c r="AA166" s="9"/>
-      <c r="AB166" s="9"/>
-      <c r="AC166" s="9"/>
-      <c r="AD166" s="6"/>
-      <c r="AE166" s="6"/>
-      <c r="AF166" s="6"/>
-      <c r="AG166" s="6"/>
-      <c r="AH166" s="6"/>
-      <c r="AI166" s="6"/>
-      <c r="AJ166" s="6"/>
-      <c r="AK166" s="6"/>
-      <c r="AL166" s="6"/>
-      <c r="AM166" s="6"/>
-      <c r="AN166" s="9"/>
-      <c r="AO166" s="6"/>
+      <c r="M166" s="5">
+        <v>10416.530000000001</v>
+      </c>
+      <c r="N166" s="6">
+        <v>91</v>
+      </c>
+      <c r="O166" s="6">
+        <v>57</v>
+      </c>
+      <c r="P166" s="7">
+        <v>5.295470652173913</v>
+      </c>
+      <c r="Q166" s="8">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="R166" s="8">
+        <v>23.378363157894739</v>
+      </c>
+      <c r="S166" s="8">
+        <v>7</v>
+      </c>
+      <c r="T166" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="U166" s="9">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="V166" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="W166" s="9">
+        <v>0</v>
+      </c>
+      <c r="X166" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="Y166" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="AD166" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF166" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH166" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL166" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM166" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN166" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO166" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP166" s="4">
         <v>58</v>
       </c>
@@ -26742,7 +28196,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -26772,35 +28226,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>2457.8000000000002</v>
+      </c>
+      <c r="N180" s="6">
+        <v>28</v>
+      </c>
+      <c r="O180" s="6">
+        <v>11</v>
+      </c>
+      <c r="P180" s="7">
+        <v>6.9022999999999994</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>18.18939090909091</v>
+      </c>
+      <c r="R180" s="8">
+        <v>3.0949999999999998</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -26841,7 +28353,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26871,35 +28383,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>8010.5299999999997</v>
+      </c>
+      <c r="N181" s="6">
+        <v>81</v>
+      </c>
+      <c r="O181" s="6">
+        <v>51</v>
+      </c>
+      <c r="P181" s="7">
+        <v>4.54032962962963</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>20.192516326530612</v>
+      </c>
+      <c r="R181" s="8">
+        <v>10.997807894736843</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.53061224489795922</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.43137254901960786</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>23</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27667,7 +29237,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27697,35 +29267,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>2514</v>
+      </c>
+      <c r="N187" s="6">
+        <v>32</v>
+      </c>
+      <c r="O187" s="6">
+        <v>25</v>
+      </c>
+      <c r="P187" s="7">
+        <v>9.1473968750000001</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>23.388000000000002</v>
+      </c>
+      <c r="R187" s="8">
+        <v>7.0939999999999994</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27766,7 +29394,7 @@
         <v>19928</v>
       </c>
       <c r="B188" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C188" s="4">
         <v>51</v>
@@ -27796,35 +29424,93 @@
         <v>58</v>
       </c>
       <c r="L188" s="4"/>
-      <c r="M188" s="5"/>
-      <c r="N188" s="6"/>
-      <c r="O188" s="6"/>
-      <c r="P188" s="7"/>
-      <c r="Q188" s="8"/>
-      <c r="R188" s="8"/>
-      <c r="S188" s="8"/>
-      <c r="T188" s="9"/>
-      <c r="U188" s="9"/>
-      <c r="V188" s="9"/>
-      <c r="W188" s="9"/>
-      <c r="X188" s="9"/>
-      <c r="Y188" s="9"/>
-      <c r="Z188" s="9"/>
-      <c r="AA188" s="9"/>
-      <c r="AB188" s="9"/>
-      <c r="AC188" s="9"/>
-      <c r="AD188" s="6"/>
-      <c r="AE188" s="6"/>
-      <c r="AF188" s="6"/>
-      <c r="AG188" s="6"/>
-      <c r="AH188" s="6"/>
-      <c r="AI188" s="6"/>
-      <c r="AJ188" s="6"/>
-      <c r="AK188" s="6"/>
-      <c r="AL188" s="6"/>
-      <c r="AM188" s="6"/>
-      <c r="AN188" s="9"/>
-      <c r="AO188" s="6"/>
+      <c r="M188" s="5">
+        <v>6540.9799999999996</v>
+      </c>
+      <c r="N188" s="6">
+        <v>69</v>
+      </c>
+      <c r="O188" s="6">
+        <v>51</v>
+      </c>
+      <c r="P188" s="7">
+        <v>4.2519042857142857</v>
+      </c>
+      <c r="Q188" s="8">
+        <v>21.862092156862744</v>
+      </c>
+      <c r="R188" s="8">
+        <v>10.975334</v>
+      </c>
+      <c r="S188" s="8">
+        <v>7</v>
+      </c>
+      <c r="T188" s="9">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="U188" s="9">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="V188" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="W188" s="9">
+        <v>0.019607843137000001</v>
+      </c>
+      <c r="X188" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y188" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA188" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AB188" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AC188" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AD188" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE188" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF188" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG188" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH188" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI188" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ188" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK188" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL188" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM188" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN188" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO188" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP188" s="4">
         <v>58</v>
       </c>
@@ -27865,7 +29551,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27895,35 +29581,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>5989.6700000000001</v>
+      </c>
+      <c r="N189" s="6">
+        <v>89</v>
+      </c>
+      <c r="O189" s="6">
+        <v>80</v>
+      </c>
+      <c r="P189" s="7">
+        <v>4.4505494505494507</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>21.949791250000001</v>
+      </c>
+      <c r="R189" s="8">
+        <v>10.990811538461539</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.21249999999999999</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.012500000000000001</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>46</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>41</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>37</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -27964,7 +29708,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -27994,35 +29738,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>12868.709999999999</v>
+      </c>
+      <c r="N190" s="6">
+        <v>126</v>
+      </c>
+      <c r="O190" s="6">
+        <v>67</v>
+      </c>
+      <c r="P190" s="7">
+        <v>7.6042968750000002</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>38.220646268656715</v>
+      </c>
+      <c r="R190" s="8">
+        <v>23.597980303030301</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0.044776119402985072</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -28532,7 +30334,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>51</v>
@@ -28562,35 +30364,93 @@
         <v>58</v>
       </c>
       <c r="L194" s="4"/>
-      <c r="M194" s="5"/>
-      <c r="N194" s="6"/>
-      <c r="O194" s="6"/>
-      <c r="P194" s="7"/>
-      <c r="Q194" s="8"/>
-      <c r="R194" s="8"/>
-      <c r="S194" s="8"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
-      <c r="V194" s="9"/>
-      <c r="W194" s="9"/>
-      <c r="X194" s="9"/>
-      <c r="Y194" s="9"/>
-      <c r="Z194" s="9"/>
-      <c r="AA194" s="9"/>
-      <c r="AB194" s="9"/>
-      <c r="AC194" s="9"/>
-      <c r="AD194" s="6"/>
-      <c r="AE194" s="6"/>
-      <c r="AF194" s="6"/>
-      <c r="AG194" s="6"/>
-      <c r="AH194" s="6"/>
-      <c r="AI194" s="6"/>
-      <c r="AJ194" s="6"/>
-      <c r="AK194" s="6"/>
-      <c r="AL194" s="6"/>
-      <c r="AM194" s="6"/>
-      <c r="AN194" s="9"/>
-      <c r="AO194" s="6"/>
+      <c r="M194" s="5">
+        <v>6067.1700000000001</v>
+      </c>
+      <c r="N194" s="6">
+        <v>67</v>
+      </c>
+      <c r="O194" s="6">
+        <v>47</v>
+      </c>
+      <c r="P194" s="7">
+        <v>13.267164179104478</v>
+      </c>
+      <c r="Q194" s="8">
+        <v>46.274815555555556</v>
+      </c>
+      <c r="R194" s="8">
+        <v>24.657406666666667</v>
+      </c>
+      <c r="S194" s="8">
+        <v>7</v>
+      </c>
+      <c r="T194" s="9">
+        <v>0</v>
+      </c>
+      <c r="U194" s="9">
+        <v>0.38297872340425532</v>
+      </c>
+      <c r="V194" s="9">
+        <v>0.085106382978723402</v>
+      </c>
+      <c r="W194" s="9">
+        <v>0</v>
+      </c>
+      <c r="X194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AB194" s="9">
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="AC194" s="9">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="AD194" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF194" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK194" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL194" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM194" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO194" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP194" s="4">
         <v>58</v>
       </c>
@@ -28631,7 +30491,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -28661,35 +30521,93 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
-      <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
-      <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="M195" s="5">
+        <v>13556.26</v>
+      </c>
+      <c r="N195" s="6">
+        <v>137</v>
+      </c>
+      <c r="O195" s="6">
+        <v>96</v>
+      </c>
+      <c r="P195" s="7">
+        <v>7.3717174242424237</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>27.475346875</v>
+      </c>
+      <c r="R195" s="8">
+        <v>13.218055208333332</v>
+      </c>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
+      <c r="T195" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="U195" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -29358,7 +31276,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29388,35 +31306,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>3129.3499999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>37</v>
+      </c>
+      <c r="O200" s="6">
+        <v>25</v>
+      </c>
+      <c r="P200" s="7">
+        <v>7.5508763157894734</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>20.781332000000003</v>
+      </c>
+      <c r="R200" s="8">
+        <v>6.1459999999999999</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.32000000000000001</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -30126,7 +32102,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -30156,35 +32132,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>4237.71</v>
+      </c>
+      <c r="N206" s="6">
+        <v>52</v>
+      </c>
+      <c r="O206" s="6">
+        <v>22</v>
+      </c>
+      <c r="P206" s="7">
+        <v>8.7277770833333328</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>22.878786363636365</v>
+      </c>
+      <c r="R206" s="8">
+        <v>7.5800000000000001</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
@@ -30225,7 +32259,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -30255,35 +32289,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>3901.8099999999999</v>
+      </c>
+      <c r="N207" s="6">
+        <v>43</v>
+      </c>
+      <c r="O207" s="6">
+        <v>18</v>
+      </c>
+      <c r="P207" s="7">
+        <v>17.558129268292682</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>37.42592777777778</v>
+      </c>
+      <c r="R207" s="8">
+        <v>16.568516666666667</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
@@ -31279,37 +33371,37 @@
         <v>320</v>
       </c>
       <c t="s" r="Y216" s="11">
+        <v>318</v>
+      </c>
+      <c t="s" r="Z216" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="AA216" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="AB216" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AC216" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AD216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>330</v>
-      </c>
-      <c t="s" r="AI216" s="11">
-        <v>310</v>
       </c>
       <c t="s" r="AJ216" s="11">
         <v>331</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 9.770,71</t>
-  </si>
-  <si>
-    <t>101.9</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.747,37</t>
+  </si>
+  <si>
+    <t>101.8</t>
   </si>
   <si>
     <t>69.5</t>
   </si>
   <si>
-    <t>7.17</t>
+    <t>7.16</t>
   </si>
   <si>
     <t>23.2</t>
@@ -959,10 +959,10 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>27.4%</t>
-  </si>
-  <si>
-    <t>15.9%</t>
+    <t>27.3%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -977,7 +977,7 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.6%</t>
+    <t>5.5%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -986,10 +986,10 @@
     <t>4.8%</t>
   </si>
   <si>
-    <t>2411.0</t>
-  </si>
-  <si>
-    <t>2020.0</t>
+    <t>2420.0</t>
+  </si>
+  <si>
+    <t>2028.0</t>
   </si>
   <si>
     <t>145.0</t>
@@ -998,7 +998,7 @@
     <t>53.0</t>
   </si>
   <si>
-    <t>378.0</t>
+    <t>380.0</t>
   </si>
   <si>
     <t>137.0</t>
@@ -1007,13 +1007,13 @@
     <t>24.0</t>
   </si>
   <si>
-    <t>707.0</t>
+    <t>709.0</t>
   </si>
   <si>
     <t>292.0</t>
   </si>
   <si>
-    <t>614.0</t>
+    <t>619.0</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -6728,7 +6728,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6758,35 +6758,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>7659.2700000000004</v>
+      </c>
+      <c r="N36" s="6">
+        <v>99</v>
+      </c>
+      <c r="O36" s="6">
+        <v>65</v>
+      </c>
+      <c r="P36" s="7">
+        <v>8.0005319148936174</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>25.131538461538462</v>
+      </c>
+      <c r="R36" s="8">
+        <v>9.5220507692307699</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7610,7 +7668,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7640,35 +7698,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>7587.6499999999996</v>
+      </c>
+      <c r="N42" s="6">
+        <v>78</v>
+      </c>
+      <c r="O42" s="6">
+        <v>68</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.488034615384616</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.142401470588233</v>
+      </c>
+      <c r="R42" s="8">
+        <v>8.9704545454545439</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.16176470588235295</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.073529411764705885</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
@@ -932,22 +932,25 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 9.747,37</t>
-  </si>
-  <si>
-    <t>101.8</t>
-  </si>
-  <si>
-    <t>69.5</t>
-  </si>
-  <si>
-    <t>7.16</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 9.760,46</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>69.8</t>
+  </si>
+  <si>
+    <t>7.18</t>
   </si>
   <si>
     <t>23.2</t>
@@ -956,13 +959,13 @@
     <t>9.3</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>27.3%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>27.0%</t>
+  </si>
+  <si>
+    <t>15.9%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -971,34 +974,37 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>3.0%</t>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
+    <t>5.6%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
   </si>
   <si>
     <t>4.8%</t>
   </si>
   <si>
-    <t>2420.0</t>
-  </si>
-  <si>
-    <t>2028.0</t>
+    <t>2488.0</t>
+  </si>
+  <si>
+    <t>2092.0</t>
   </si>
   <si>
     <t>145.0</t>
   </si>
   <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>380.0</t>
+    <t>54.0</t>
+  </si>
+  <si>
+    <t>381.0</t>
   </si>
   <si>
     <t>137.0</t>
@@ -1007,19 +1013,19 @@
     <t>24.0</t>
   </si>
   <si>
-    <t>709.0</t>
-  </si>
-  <si>
-    <t>292.0</t>
-  </si>
-  <si>
-    <t>619.0</t>
+    <t>733.0</t>
+  </si>
+  <si>
+    <t>316.0</t>
+  </si>
+  <si>
+    <t>637.0</t>
   </si>
   <si>
     <t>0.9%</t>
   </si>
   <si>
-    <t>114.0</t>
+    <t>115.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6472,7 +6478,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6502,35 +6508,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>16195.17</v>
+      </c>
+      <c r="N34" s="6">
+        <v>178</v>
+      </c>
+      <c r="O34" s="6">
+        <v>139</v>
+      </c>
+      <c r="P34" s="7">
+        <v>13.005179096045199</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>21.730455395683453</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.4621556390977446</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.17266187050359713</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.25899280575539568</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.071942446043165464</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.15827338129496402</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.028776978417266189</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>36</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>36</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>22</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -18678,33 +18742,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>51</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.25490196078431371</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.19607843137254902</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22445,7 +22555,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22475,35 +22585,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>5733.9499999999998</v>
+      </c>
+      <c r="N141" s="6">
+        <v>71</v>
+      </c>
+      <c r="O141" s="6">
+        <v>48</v>
+      </c>
+      <c r="P141" s="7">
+        <v>4.4628014492753616</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>14.739583333333334</v>
+      </c>
+      <c r="R141" s="8">
+        <v>4.4801810810810805</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.6875</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>11</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33434,137 +33602,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>87</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.045977011494252873</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0.011494252873</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
-        <v>318</v>
-      </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AA217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c t="s" r="AO217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>339</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>339</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 9.760,46</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 9.765,65</t>
   </si>
   <si>
     <t>102.0</t>
@@ -950,13 +950,13 @@
     <t>69.8</t>
   </si>
   <si>
-    <t>7.18</t>
-  </si>
-  <si>
-    <t>23.2</t>
-  </si>
-  <si>
-    <t>9.3</t>
+    <t>7.20</t>
+  </si>
+  <si>
+    <t>23.3</t>
+  </si>
+  <si>
+    <t>9.4</t>
   </si>
   <si>
     <t>6.3</t>
@@ -14783,7 +14783,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14811,14 +14811,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10732.26</v>
+      </c>
+      <c r="N89" s="6">
+        <v>99</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>11.366666666666665</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>51.882222222222218</v>
+      </c>
+      <c r="R89" s="8">
+        <v>32.437777777777782</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29265,7 +29277,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31973,7 +31985,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33606,7 +33618,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-04).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>26</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 9.765,65</t>
+    <t>R$ 9.661,07</t>
   </si>
   <si>
-    <t>102.0</t>
+    <t>101.0</t>
   </si>
   <si>
-    <t>69.8</t>
+    <t>69.6</t>
   </si>
   <si>
-    <t>7.20</t>
+    <t>7.16</t>
   </si>
   <si>
-    <t>23.3</t>
+    <t>23.4</t>
   </si>
   <si>
-    <t>9.4</t>
+    <t>9.5</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>27.0%</t>
+    <t>27.1%</t>
   </si>
   <si>
-    <t>15.9%</t>
+    <t>15.6%</t>
   </si>
   <si>
     <t>1.1%</t>
@@ -983,28 +983,28 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.6%</t>
+    <t>5.5%</t>
   </si>
   <si>
     <t>2.4%</t>
   </si>
   <si>
-    <t>4.8%</t>
+    <t>4.7%</t>
   </si>
   <si>
-    <t>2488.0</t>
+    <t>2497.0</t>
   </si>
   <si>
-    <t>2092.0</t>
+    <t>2101.0</t>
   </si>
   <si>
-    <t>145.0</t>
+    <t>148.0</t>
   </si>
   <si>
     <t>54.0</t>
   </si>
   <si>
-    <t>381.0</t>
+    <t>383.0</t>
   </si>
   <si>
     <t>137.0</t>
@@ -1013,10 +1013,10 @@
     <t>24.0</t>
   </si>
   <si>
-    <t>733.0</t>
+    <t>734.0</t>
   </si>
   <si>
-    <t>316.0</t>
+    <t>317.0</t>
   </si>
   <si>
     <t>637.0</t>
@@ -1025,7 +1025,7 @@
     <t>0.9%</t>
   </si>
   <si>
-    <t>115.0</t>
+    <t>117.0</t>
   </si>
   <si>
     <t>1</t>
@@ -9139,7 +9139,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9169,14 +9169,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1784.7</v>
+      </c>
+      <c r="N51" s="6">
+        <v>19</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>1.7675421052631579</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>51.9020875</v>
+      </c>
+      <c r="R51" s="8">
+        <v>58.419450000000005</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.25</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10208,33 +10220,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>100</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24131,7 +24189,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24161,35 +24219,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>6454.1599999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>80</v>
+      </c>
+      <c r="O151" s="6">
+        <v>70</v>
+      </c>
+      <c r="P151" s="7">
+        <v>7.2047912499999995</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>17.729047142857144</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.5833333333333335</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.41428571428571431</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25013,7 +25129,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25043,35 +25159,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>5588.0799999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>57</v>
+      </c>
+      <c r="O157" s="6">
+        <v>47</v>
+      </c>
+      <c r="P157" s="7">
+        <v>6.7847947368421053</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>17.486878723404253</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.8148936170212768</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.40425531914893614</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -26203,7 +26377,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26233,35 +26407,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>5260.5600000000004</v>
+      </c>
+      <c r="N165" s="6">
+        <v>51</v>
+      </c>
+      <c r="O165" s="6">
+        <v>32</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.5724365384615382</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>14.351040625</v>
+      </c>
+      <c r="R165" s="8">
+        <v>2.1526031250000002</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
